--- a/ALCORTA 146/Octubre/Octubre.xlsx
+++ b/ALCORTA 146/Octubre/Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ALCORTA 146\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23CDAA3-36B3-448F-A2D3-666A85517A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BBDA5D-958B-49F6-B4F6-15F9AC4972ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$C$1:$O$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Recibo '!$E$6:$N$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="196">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -389,9 +389,6 @@
     <t>b</t>
   </si>
   <si>
-    <t>ARBA</t>
-  </si>
-  <si>
     <t xml:space="preserve">EDESUR Nro de cliente : 01121995   </t>
   </si>
   <si>
@@ -423,9 +420,6 @@
   </si>
   <si>
     <t>HONORARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustavo Padron </t>
   </si>
   <si>
     <t>HONORARIOS administracion</t>
@@ -573,33 +567,6 @@
     <t>Efectivo</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Cerrajeria Walter - Limpiador de acero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fumigacion </t>
-  </si>
-  <si>
-    <t>ARCA - Parte de deuda</t>
-  </si>
-  <si>
-    <t>Envio carta documento 4D</t>
-  </si>
-  <si>
-    <t>Carta documento 4D - Honorarios</t>
-  </si>
-  <si>
-    <t>Plan de pagos vigente</t>
-  </si>
-  <si>
-    <t>Carta documento 6D- Honorarios</t>
-  </si>
-  <si>
-    <t>Envio carta documento 6D</t>
-  </si>
-  <si>
     <t>VTO 14/11</t>
   </si>
   <si>
@@ -615,10 +582,40 @@
     <t>Metrogas OCTUBRE</t>
   </si>
   <si>
-    <t>Pastorizza - 14/10</t>
-  </si>
-  <si>
     <t>Cuota 10</t>
+  </si>
+  <si>
+    <t>Servicio de fumigacion - Sr. Pastorizza</t>
+  </si>
+  <si>
+    <t>Pago a abogado - Acuerdo final SUTHER</t>
+  </si>
+  <si>
+    <t>ARBA - Pago de deuda total</t>
+  </si>
+  <si>
+    <t>Gustavo Padron - cierre de SUTHER</t>
+  </si>
+  <si>
+    <t>FATHERY - Sindicato</t>
+  </si>
+  <si>
+    <t>SUTHER - Sindicato</t>
+  </si>
+  <si>
+    <t>SERACARH - Sindicato</t>
+  </si>
+  <si>
+    <t>Acuerdo deuda de 6D</t>
+  </si>
+  <si>
+    <t>Plan de pagos vigente  -3A</t>
+  </si>
+  <si>
+    <t>Plan de pagos vigente - 6D</t>
+  </si>
+  <si>
+    <t>Conciliacion cochera edificio - COCH 9</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1440,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1541,8 +1538,6 @@
     <xf numFmtId="44" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1608,7 +1603,6 @@
     <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1670,6 +1664,27 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1678,12 +1693,6 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1699,21 +1708,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1738,9 +1732,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2106,38 +2098,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M122"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="57"/>
       <c r="B1" s="58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
       <c r="E1" s="57"/>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="59"/>
       <c r="B2" s="60" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
       <c r="E2" s="62"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="63"/>
       <c r="B3" s="64" t="s">
         <v>46</v>
@@ -2146,47 +2138,47 @@
       <c r="D3" s="64"/>
       <c r="E3" s="65"/>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="63"/>
       <c r="B4" s="64" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D4" s="64"/>
       <c r="E4" s="65"/>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="63"/>
       <c r="B5" s="64" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
       <c r="E5" s="65"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="67" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="63"/>
       <c r="B7" s="64"/>
       <c r="C7" s="64"/>
       <c r="D7" s="64"/>
       <c r="E7" s="65"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
         <v>45</v>
       </c>
@@ -2195,142 +2187,142 @@
       <c r="D8" s="67"/>
       <c r="E8" s="68"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="69"/>
       <c r="B9" s="69"/>
       <c r="C9" s="69"/>
       <c r="D9" s="69"/>
       <c r="E9" s="69"/>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="69"/>
       <c r="B10" s="69"/>
       <c r="C10" s="69"/>
       <c r="D10" s="69"/>
       <c r="E10" s="69"/>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
       <c r="B11" s="69"/>
       <c r="C11" s="69"/>
       <c r="D11" s="69"/>
       <c r="E11" s="69"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="69"/>
       <c r="B12" s="69"/>
       <c r="C12" s="69"/>
       <c r="D12" s="69"/>
       <c r="E12" s="69"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="69"/>
       <c r="B13" s="69"/>
       <c r="C13" s="69"/>
       <c r="D13" s="69"/>
       <c r="E13" s="69"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="69"/>
       <c r="B14" s="69"/>
       <c r="C14" s="69"/>
       <c r="D14" s="69"/>
       <c r="E14" s="69"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="157" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="157"/>
-      <c r="B16" s="157"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="157"/>
-      <c r="B17" s="157"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="157"/>
-      <c r="B18" s="157"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="154" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="154"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+    </row>
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69"/>
       <c r="B19" s="69"/>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
       <c r="E19" s="69"/>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69"/>
       <c r="B20" s="69"/>
       <c r="C20" s="69"/>
       <c r="D20" s="69"/>
       <c r="E20" s="69"/>
     </row>
-    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="69"/>
       <c r="B21" s="69"/>
       <c r="C21" s="69"/>
       <c r="D21" s="69"/>
       <c r="E21" s="69"/>
     </row>
-    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="158"/>
-      <c r="B22" s="159"/>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="159"/>
-      <c r="B23" s="159"/>
-      <c r="C23" s="159"/>
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="159"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="159"/>
-      <c r="B25" s="159"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="159"/>
-      <c r="B26" s="159"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="155"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="156"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="156"/>
+      <c r="B24" s="156"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="156"/>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="156"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="156"/>
+      <c r="B26" s="156"/>
+      <c r="C26" s="156"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="69"/>
       <c r="B27" s="69"/>
       <c r="C27" s="69"/>
       <c r="D27" s="69"/>
       <c r="E27" s="69"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="70" t="s">
         <v>32</v>
       </c>
@@ -2339,7 +2331,7 @@
       <c r="D28" s="73"/>
       <c r="E28" s="74"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>114</v>
       </c>
@@ -2348,30 +2340,30 @@
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
     </row>
-    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B30" s="76"/>
       <c r="C30" s="76"/>
       <c r="D30" s="77"/>
       <c r="E30" s="76"/>
     </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="75"/>
-      <c r="B31" s="137"/>
+      <c r="B31" s="135"/>
       <c r="C31" s="76"/>
       <c r="D31" s="77"/>
       <c r="E31" s="76"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="75"/>
       <c r="B32" s="76"/>
       <c r="C32" s="76"/>
       <c r="D32" s="77"/>
       <c r="E32" s="76"/>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
         <v>1</v>
       </c>
@@ -2383,14 +2375,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76"/>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
       <c r="D34" s="77"/>
       <c r="E34" s="76"/>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="76"/>
       <c r="B35" s="76"/>
       <c r="C35" s="76"/>
@@ -2398,16 +2390,16 @@
       <c r="E35" s="76"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="76"/>
       <c r="B36" s="76"/>
       <c r="C36" s="76"/>
       <c r="D36" s="80"/>
       <c r="E36" s="76"/>
     </row>
-    <row r="37" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -2418,54 +2410,54 @@
       </c>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
       <c r="D38" s="21"/>
       <c r="E38" s="81"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="76" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C39" s="76"/>
-      <c r="D39" s="77">
-        <v>30000</v>
+      <c r="D39" s="17">
+        <v>50000</v>
       </c>
       <c r="E39" s="82"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="76" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C40" s="76"/>
       <c r="D40" s="77">
         <v>123100</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="76"/>
       <c r="B41" s="76"/>
       <c r="C41" s="76"/>
       <c r="D41" s="17"/>
       <c r="E41" s="82"/>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
         <v>110</v>
       </c>
@@ -2474,10 +2466,10 @@
       <c r="D42" s="25"/>
       <c r="E42" s="83">
         <f>SUM(D39:D40)</f>
-        <v>153100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>173100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>2</v>
       </c>
@@ -2486,27 +2478,31 @@
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B44" s="76"/>
       <c r="C44" s="76" t="s">
-        <v>196</v>
-      </c>
-      <c r="D44" s="141">
-        <v>25852</v>
+        <v>184</v>
+      </c>
+      <c r="D44" s="17">
+        <v>29900</v>
       </c>
       <c r="E44" s="24"/>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="75"/>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="75" t="s">
+        <v>187</v>
+      </c>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
-      <c r="D45" s="17"/>
+      <c r="D45" s="17">
+        <v>359837.6</v>
+      </c>
       <c r="E45" s="84"/>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>3</v>
       </c>
@@ -2514,11 +2510,11 @@
       <c r="C46" s="20"/>
       <c r="D46" s="25"/>
       <c r="E46" s="85">
-        <f>SUM(D44)</f>
-        <v>25852</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <f>SUM(D44:D45)</f>
+        <v>389737.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>111</v>
       </c>
@@ -2527,756 +2523,727 @@
       <c r="D47" s="26"/>
       <c r="E47" s="86"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
       <c r="D48" s="17">
-        <v>1124286.96</v>
+        <v>54153.08</v>
       </c>
       <c r="E48" s="24"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="76"/>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="76" t="s">
+        <v>189</v>
+      </c>
       <c r="B49" s="76"/>
       <c r="C49" s="76"/>
-      <c r="D49" s="17"/>
+      <c r="D49" s="17">
+        <v>30852.35</v>
+      </c>
       <c r="E49" s="24"/>
     </row>
-    <row r="50" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="20" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="76" t="s">
+        <v>191</v>
+      </c>
+      <c r="B50" s="76"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="17">
+        <v>4595.4799999999996</v>
+      </c>
+      <c r="E50" s="24"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="76" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="17">
+        <v>414980.03</v>
+      </c>
+      <c r="E51" s="24"/>
+    </row>
+    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="87">
-        <f>SUM(D48:D49)</f>
-        <v>1124286.96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="87">
+        <f>SUM(D48:D51)</f>
+        <v>504580.94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="86"/>
-    </row>
-    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="B52" s="88"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="141">
-        <v>491388.19</v>
-      </c>
-      <c r="E52" s="24"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="88" t="s">
-        <v>165</v>
-      </c>
-      <c r="B53" s="88"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="141">
-        <v>75500</v>
-      </c>
-      <c r="E53" s="17"/>
-    </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="86"/>
+    </row>
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="88"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="17">
+        <v>501470.06</v>
+      </c>
+      <c r="E54" s="24"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="88"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="17">
+        <v>77500</v>
+      </c>
+      <c r="E55" s="17"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="88" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="92"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="17">
+        <v>73000</v>
+      </c>
+      <c r="E56" s="24"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="76"/>
+      <c r="C57" s="137"/>
+      <c r="D57" s="152">
+        <v>0</v>
+      </c>
+      <c r="E57" s="24"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="76"/>
+      <c r="C58" s="138"/>
+      <c r="D58" s="152">
+        <v>0</v>
+      </c>
+      <c r="E58" s="82"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="76"/>
+      <c r="C59" s="138"/>
+      <c r="D59" s="152">
+        <v>0</v>
+      </c>
+      <c r="E59" s="82"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="76" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="89"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="17">
-        <v>0</v>
-      </c>
-      <c r="E54" s="24"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="76" t="s">
+      <c r="B60" s="76"/>
+      <c r="C60" s="138"/>
+      <c r="D60" s="152">
+        <v>0</v>
+      </c>
+      <c r="E60" s="82"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="76"/>
+      <c r="C61" s="138"/>
+      <c r="D61" s="152">
+        <v>0</v>
+      </c>
+      <c r="E61" s="137"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="76" t="s">
         <v>183</v>
       </c>
-      <c r="B55" s="76"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="17">
-        <v>95000</v>
-      </c>
-      <c r="E55" s="24"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="76" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="76"/>
-      <c r="C56" s="139"/>
-      <c r="D56" s="155">
-        <v>111255.93</v>
-      </c>
-      <c r="E56" s="24"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="76" t="s">
-        <v>140</v>
-      </c>
-      <c r="B57" s="76"/>
-      <c r="C57" s="141"/>
-      <c r="D57" s="17">
-        <v>110899</v>
-      </c>
-      <c r="E57" s="82"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="76"/>
-      <c r="C58" s="141"/>
-      <c r="D58" s="17">
-        <v>15455.5</v>
-      </c>
-      <c r="E58" s="82" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="76"/>
-      <c r="C59" s="141"/>
-      <c r="D59" s="17">
-        <v>3535.19</v>
-      </c>
-      <c r="E59" s="82"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="141"/>
-      <c r="D60" s="17">
-        <v>7462.34</v>
-      </c>
-      <c r="E60" s="139"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="76" t="s">
-        <v>194</v>
-      </c>
-      <c r="B61" s="76"/>
-      <c r="C61" s="76"/>
-      <c r="D61" s="141">
+      <c r="B62" s="76"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="17">
         <v>5512.37</v>
       </c>
-      <c r="E61" s="24"/>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="76"/>
-      <c r="B62" s="91"/>
-      <c r="C62" s="92"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="84"/>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="20" t="s">
+      <c r="E62" s="24"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="76"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="84"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="20" t="s">
         <v>5</v>
-      </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="85">
-        <f>SUM(D52:D62)</f>
-        <v>916008.51999999979</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="19" t="s">
-        <v>112</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="25"/>
-      <c r="E64" s="85"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="76" t="s">
-        <v>147</v>
-      </c>
-      <c r="B65" s="76"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="17">
+      <c r="E64" s="85">
+        <f>SUM(D54:D63)</f>
+        <v>657482.43000000005</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="85"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="76" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="76"/>
+      <c r="C66" s="76"/>
+      <c r="D66" s="17">
         <v>49294.58</v>
       </c>
-      <c r="E65" s="82"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="198" t="s">
-        <v>195</v>
-      </c>
-      <c r="B66" s="198"/>
-      <c r="C66" s="198"/>
-      <c r="D66" s="199"/>
-      <c r="E66" s="200"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E66" s="82"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="76" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="B67" s="76"/>
       <c r="C67" s="76"/>
-      <c r="D67" s="17">
-        <v>22000</v>
-      </c>
-      <c r="E67" s="82"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="76" t="s">
-        <v>181</v>
-      </c>
-      <c r="B68" s="76"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="17">
-        <f>135700</f>
-        <v>135700</v>
-      </c>
-      <c r="E68" s="82"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="76" t="s">
-        <v>139</v>
-      </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="24">
-        <v>2400</v>
-      </c>
-      <c r="E69" s="24"/>
-    </row>
-    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="20" t="s">
+      <c r="D67" s="24">
+        <v>2700</v>
+      </c>
+      <c r="E67" s="24"/>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="93">
-        <f>SUM(D65:D69)</f>
-        <v>209394.58000000002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="19" t="s">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="91">
+        <f>SUM(D66:D67)</f>
+        <v>51994.58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="85"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="76" t="s">
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="85"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="B72" s="76"/>
-      <c r="C72" s="76"/>
-      <c r="D72" s="17">
-        <v>67395.62</v>
-      </c>
-      <c r="E72" s="94"/>
-    </row>
-    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="75"/>
+      <c r="B70" s="76"/>
+      <c r="C70" s="76"/>
+      <c r="D70" s="17">
+        <v>50446.16</v>
+      </c>
+      <c r="E70" s="92"/>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="75"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="76"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="93"/>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="85">
+        <f>SUM(D70:D71)</f>
+        <v>50446.16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="76"/>
       <c r="B73" s="76"/>
       <c r="C73" s="76"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="95"/>
-    </row>
-    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="85">
-        <f>SUM(D72:D73)</f>
-        <v>67395.62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="76"/>
-      <c r="B75" s="76"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="76"/>
-      <c r="E75" s="96"/>
-    </row>
-    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="B76" s="97"/>
-      <c r="C76" s="97"/>
-      <c r="D76" s="98"/>
-      <c r="E76" s="99">
-        <f>5100000-2500375.29</f>
-        <v>2599624.71</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="100"/>
+      <c r="D73" s="76"/>
+      <c r="E73" s="94"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="95"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="97">
+        <f>4100000-1827341.71</f>
+        <v>2272658.29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="98"/>
+      <c r="B75" s="69"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="31"/>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="100" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="101"/>
+      <c r="C76" s="102"/>
+      <c r="D76" s="102"/>
+      <c r="E76" s="103">
+        <f>(SUM(E30:E74))</f>
+        <v>4100000</v>
+      </c>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="69"/>
       <c r="B77" s="69"/>
       <c r="C77" s="69"/>
       <c r="D77" s="69"/>
-      <c r="E77" s="101"/>
-      <c r="F77" s="31"/>
-    </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" s="103"/>
-      <c r="C78" s="104"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="105">
-        <f>(SUM(E30:E76))</f>
-        <v>5095662.3899999997</v>
-      </c>
+      <c r="E77" s="69"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="69"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="69"/>
       <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="69"/>
-      <c r="B79" s="69"/>
-      <c r="C79" s="69"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="165" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" s="166"/>
+      <c r="C79" s="104"/>
       <c r="D79" s="69"/>
       <c r="E79" s="69"/>
     </row>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="69"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="69"/>
+    <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="157"/>
+      <c r="B80" s="158"/>
+      <c r="C80" s="17"/>
       <c r="D80" s="69"/>
       <c r="E80" s="69"/>
-      <c r="F80" s="31"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="168" t="s">
-        <v>143</v>
-      </c>
-      <c r="B81" s="169"/>
-      <c r="C81" s="106"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="159"/>
+      <c r="B81" s="160"/>
+      <c r="C81" s="17"/>
       <c r="D81" s="69"/>
       <c r="E81" s="69"/>
     </row>
-    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="160"/>
-      <c r="B82" s="161"/>
-      <c r="C82" s="17"/>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="161"/>
+      <c r="B82" s="162"/>
+      <c r="C82" s="105"/>
       <c r="D82" s="69"/>
-      <c r="E82" s="69"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="162"/>
-      <c r="B83" s="163"/>
-      <c r="C83" s="17"/>
+      <c r="E82" s="106"/>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="163" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="164"/>
+      <c r="C83" s="107">
+        <f>SUM(C80:C82)</f>
+        <v>0</v>
+      </c>
       <c r="D83" s="69"/>
       <c r="E83" s="69"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="164"/>
-      <c r="B84" s="165"/>
-      <c r="C84" s="107"/>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="69"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="69"/>
       <c r="D84" s="69"/>
-      <c r="E84" s="108"/>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="166" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" s="167"/>
-      <c r="C85" s="109">
-        <f>SUM(C82:C84)</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="69"/>
+      <c r="E84" s="69"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" s="108"/>
+      <c r="C85" s="109"/>
+      <c r="D85" s="110"/>
       <c r="E85" s="69"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="69"/>
       <c r="B86" s="69"/>
       <c r="C86" s="69"/>
       <c r="D86" s="69"/>
       <c r="E86" s="69"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="110" t="s">
-        <v>148</v>
-      </c>
-      <c r="B87" s="110"/>
-      <c r="C87" s="111"/>
-      <c r="D87" s="112"/>
-      <c r="E87" s="69"/>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="69"/>
-      <c r="B88" s="69"/>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="B87" s="112">
+        <f>E76</f>
+        <v>4100000</v>
+      </c>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="106"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="113" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" s="114">
+        <f>E76-E74</f>
+        <v>1827341.71</v>
+      </c>
       <c r="C88" s="69"/>
       <c r="D88" s="69"/>
       <c r="E88" s="69"/>
     </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="113" t="s">
-        <v>38</v>
-      </c>
-      <c r="B89" s="114">
-        <f>E78</f>
-        <v>5095662.3899999997</v>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="115" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="116">
+        <f>C83+C85</f>
+        <v>0</v>
       </c>
       <c r="C89" s="69"/>
       <c r="D89" s="69"/>
-      <c r="E89" s="108"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E89" s="69"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="115" t="s">
-        <v>39</v>
+        <v>142</v>
       </c>
       <c r="B90" s="116">
-        <f>E78-E76</f>
-        <v>2496037.6799999997</v>
+        <f>C83</f>
+        <v>0</v>
       </c>
       <c r="C90" s="69"/>
       <c r="D90" s="69"/>
       <c r="E90" s="69"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="117" t="s">
-        <v>145</v>
-      </c>
-      <c r="B91" s="118">
-        <f>C85+C87</f>
-        <v>0</v>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="115" t="s">
+        <v>144</v>
+      </c>
+      <c r="B91" s="116">
+        <f>B88+B90</f>
+        <v>1827341.71</v>
       </c>
       <c r="C91" s="69"/>
       <c r="D91" s="69"/>
       <c r="E91" s="69"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="117" t="s">
-        <v>144</v>
-      </c>
-      <c r="B92" s="118">
-        <f>C85</f>
-        <v>0</v>
-      </c>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="69"/>
+      <c r="B92" s="69"/>
       <c r="C92" s="69"/>
       <c r="D92" s="69"/>
       <c r="E92" s="69"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="117" t="s">
-        <v>146</v>
-      </c>
-      <c r="B93" s="118">
-        <f>B90+B92</f>
-        <v>2496037.6799999997</v>
-      </c>
-      <c r="C93" s="69"/>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="156"/>
+      <c r="B93" s="156"/>
+      <c r="C93" s="156"/>
       <c r="D93" s="69"/>
       <c r="E93" s="69"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="69"/>
-      <c r="B94" s="69"/>
-      <c r="C94" s="69"/>
+    <row r="94" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="156"/>
+      <c r="B94" s="156"/>
+      <c r="C94" s="156"/>
       <c r="D94" s="69"/>
       <c r="E94" s="69"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="159"/>
-      <c r="B95" s="159"/>
-      <c r="C95" s="159"/>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="69"/>
+      <c r="B95" s="69"/>
+      <c r="C95" s="69"/>
       <c r="D95" s="69"/>
       <c r="E95" s="69"/>
     </row>
-    <row r="96" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="159"/>
-      <c r="B96" s="159"/>
-      <c r="C96" s="159"/>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="B96" s="118"/>
+      <c r="C96" s="119"/>
       <c r="D96" s="69"/>
       <c r="E96" s="69"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="69"/>
-      <c r="B97" s="69"/>
-      <c r="C97" s="69"/>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" s="118">
+        <v>1103830.8583760336</v>
+      </c>
+      <c r="C97" s="120"/>
       <c r="D97" s="69"/>
       <c r="E97" s="69"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="119" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" s="120"/>
-      <c r="C98" s="121"/>
-      <c r="D98" s="69"/>
+    <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" s="122">
+        <f>PRORRATEO!I42</f>
+        <v>4711650</v>
+      </c>
+      <c r="C98" s="119"/>
+      <c r="D98" s="106"/>
       <c r="E98" s="69"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="16" t="s">
+    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="B99" s="122">
+        <v>61700</v>
+      </c>
+      <c r="C99" s="119"/>
+      <c r="D99" s="106"/>
+      <c r="E99" s="69"/>
+    </row>
+    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="121" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" s="136">
+        <v>200000</v>
+      </c>
+      <c r="C100" s="119"/>
+      <c r="D100" s="106"/>
+      <c r="E100" s="69"/>
+    </row>
+    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="121" t="s">
+        <v>195</v>
+      </c>
+      <c r="B101" s="136">
+        <f>-PRORRATEO!H38</f>
+        <v>-167279.99999999997</v>
+      </c>
+      <c r="C101" s="119"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="69"/>
+    </row>
+    <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="123" t="s">
+        <v>41</v>
+      </c>
+      <c r="B102" s="136">
+        <f>-(B91+B111)</f>
+        <v>-1704241.71</v>
+      </c>
+      <c r="C102" s="119"/>
+      <c r="D102" s="69"/>
+      <c r="E102" s="69"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="124" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" s="40">
+        <f>SUM(B97:B102)</f>
+        <v>4205659.1483760336</v>
+      </c>
+      <c r="C103" s="125"/>
+      <c r="D103" s="106"/>
+      <c r="E103" s="69"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="69"/>
+      <c r="B104" s="126"/>
+      <c r="C104" s="125"/>
+      <c r="D104" s="69"/>
+      <c r="E104" s="69"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="69"/>
+      <c r="B105" s="127"/>
+      <c r="C105" s="125"/>
+      <c r="D105" s="120"/>
+      <c r="E105" s="69"/>
+    </row>
+    <row r="106" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="69"/>
+      <c r="B106" s="126"/>
+      <c r="C106" s="128"/>
+      <c r="D106" s="129"/>
+      <c r="E106" s="129"/>
+    </row>
+    <row r="107" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B107" s="24"/>
+      <c r="C107" s="128"/>
+      <c r="D107" s="129"/>
+      <c r="E107" s="131"/>
+    </row>
+    <row r="108" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B99" s="120">
-        <v>-560589.97402956639</v>
-      </c>
-      <c r="C99" s="122"/>
-      <c r="D99" s="69"/>
-      <c r="E99" s="69"/>
-    </row>
-    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="123" t="s">
-        <v>42</v>
-      </c>
-      <c r="B100" s="124">
-        <f>PRORRATEO!I42</f>
-        <v>4055849.1224055998</v>
-      </c>
-      <c r="C100" s="121"/>
-      <c r="D100" s="108"/>
-      <c r="E100" s="69"/>
-    </row>
-    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="123" t="s">
-        <v>186</v>
-      </c>
-      <c r="B101" s="138">
-        <v>-74376</v>
-      </c>
-      <c r="C101" s="121"/>
-      <c r="D101" s="108"/>
-      <c r="E101" s="69"/>
-    </row>
-    <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="123" t="s">
-        <v>185</v>
-      </c>
-      <c r="B102" s="138">
-        <v>-19000</v>
-      </c>
-      <c r="C102" s="121"/>
-      <c r="D102" s="108"/>
-      <c r="E102" s="69"/>
-    </row>
-    <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="123" t="s">
-        <v>188</v>
-      </c>
-      <c r="B103" s="138">
-        <v>-74376</v>
-      </c>
-      <c r="C103" s="121"/>
-      <c r="D103" s="108"/>
-      <c r="E103" s="69"/>
-    </row>
-    <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="123" t="s">
-        <v>189</v>
-      </c>
-      <c r="B104" s="138">
-        <v>-19000</v>
-      </c>
-      <c r="C104" s="121"/>
-      <c r="D104" s="108"/>
-      <c r="E104" s="69"/>
-    </row>
-    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="123" t="s">
-        <v>187</v>
-      </c>
-      <c r="B105" s="138">
-        <v>61700</v>
-      </c>
-      <c r="C105" s="121"/>
-      <c r="D105" s="108"/>
-      <c r="E105" s="69"/>
-    </row>
-    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="125" t="s">
+      <c r="B108" s="24">
+        <v>53473.308601000113</v>
+      </c>
+      <c r="C108" s="128"/>
+      <c r="D108" s="131"/>
+      <c r="E108" s="131"/>
+    </row>
+    <row r="109" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="24">
+        <f>PRORRATEO!I43</f>
+        <v>169830.00000000003</v>
+      </c>
+      <c r="C109" s="125"/>
+      <c r="D109" s="106"/>
+      <c r="E109" s="69"/>
+    </row>
+    <row r="110" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="121" t="s">
+        <v>192</v>
+      </c>
+      <c r="B110" s="136">
+        <v>-115000</v>
+      </c>
+      <c r="C110" s="125"/>
+      <c r="D110" s="106"/>
+      <c r="E110" s="69"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="B106" s="138">
-        <f>-(B93+B114)</f>
-        <v>-2262038.6799999997</v>
-      </c>
-      <c r="C106" s="121"/>
-      <c r="D106" s="69"/>
-      <c r="E106" s="69"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="126" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="40">
-        <f>SUM(B99:B106)</f>
-        <v>1108168.4683760339</v>
-      </c>
-      <c r="C107" s="127"/>
-      <c r="D107" s="108"/>
-      <c r="E107" s="69"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="69"/>
-      <c r="B108" s="128"/>
-      <c r="C108" s="127"/>
-      <c r="D108" s="69"/>
-      <c r="E108" s="69"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="69"/>
-      <c r="B109" s="129"/>
-      <c r="C109" s="127"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="69"/>
-    </row>
-    <row r="110" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="69"/>
-      <c r="B110" s="128"/>
-      <c r="C110" s="130"/>
-      <c r="D110" s="131"/>
-      <c r="E110" s="131"/>
-    </row>
-    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="132" t="s">
-        <v>43</v>
-      </c>
-      <c r="B111" s="24"/>
-      <c r="C111" s="130"/>
-      <c r="D111" s="131"/>
-      <c r="E111" s="133"/>
-    </row>
-    <row r="112" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="B112" s="24">
-        <v>117641.86240000001</v>
-      </c>
-      <c r="C112" s="130"/>
-      <c r="D112" s="133"/>
-      <c r="E112" s="133"/>
-    </row>
-    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="B113" s="24">
-        <f>PRORRATEO!I43</f>
-        <v>169830.44620100007</v>
-      </c>
-      <c r="C113" s="127"/>
-      <c r="D113" s="108"/>
+      <c r="B111" s="39">
+        <f>-(D40+D58)</f>
+        <v>-123100</v>
+      </c>
+      <c r="C111" s="125"/>
+      <c r="D111" s="69"/>
+      <c r="E111" s="69"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="76"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="125"/>
+      <c r="D112" s="69"/>
+      <c r="E112" s="69"/>
+    </row>
+    <row r="113" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="135"/>
+      <c r="B113" s="134"/>
+      <c r="C113" s="132"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="69"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="B114" s="39">
-        <f>-(D40+D57)</f>
-        <v>-233999</v>
-      </c>
-      <c r="C114" s="127"/>
+    <row r="114" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="135"/>
+      <c r="B114" s="134"/>
+      <c r="C114" s="132"/>
       <c r="D114" s="69"/>
       <c r="E114" s="69"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="76"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="127"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="B115" s="40">
+        <f>SUM(B108:B114)</f>
+        <v>-14796.691398999857</v>
+      </c>
+      <c r="C115" s="119"/>
       <c r="D115" s="69"/>
       <c r="E115" s="69"/>
     </row>
-    <row r="116" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="137"/>
-      <c r="B116" s="136"/>
-      <c r="C116" s="134"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="69"/>
+      <c r="B116" s="69"/>
+      <c r="C116" s="69"/>
       <c r="D116" s="69"/>
       <c r="E116" s="69"/>
     </row>
-    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="137"/>
-      <c r="B117" s="136"/>
-      <c r="C117" s="134"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="69"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="132" t="s">
-        <v>44</v>
-      </c>
-      <c r="B118" s="40">
-        <f>SUM(B112:B117)</f>
-        <v>53473.308601000113</v>
-      </c>
-      <c r="C118" s="121"/>
-      <c r="D118" s="69"/>
-      <c r="E118" s="69"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="69"/>
-      <c r="B119" s="69"/>
-      <c r="C119" s="69"/>
-      <c r="D119" s="69"/>
-      <c r="E119" s="69"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="156" t="s">
-        <v>149</v>
-      </c>
-      <c r="B121" s="156"/>
-      <c r="C121" s="156"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="156"/>
-      <c r="B122" s="156"/>
-      <c r="C122" s="156"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="23"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="32" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="153" t="s">
+        <v>147</v>
+      </c>
+      <c r="B118" s="153"/>
+      <c r="C118" s="153"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="153"/>
+      <c r="B119" s="153"/>
+      <c r="C119" s="153"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="23"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B124" s="32"/>
-      <c r="C124" s="33">
-        <f>SUM(C123:C123)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M125" s="4"/>
+      <c r="B121" s="32"/>
+      <c r="C121" s="33">
+        <f>SUM(C120:C120)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M122" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A118:C119"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="A22:E26"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A95:C96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A93:C94"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3287,27 +3254,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
     <col min="9" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="9.88671875" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3323,13 +3290,13 @@
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="172">
-        <v>5100000</v>
-      </c>
-      <c r="O1" s="172"/>
+      <c r="N1" s="176">
+        <v>4100000</v>
+      </c>
+      <c r="O1" s="176"/>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3345,72 +3312,72 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="171"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="173" t="s">
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="180" t="s">
+      <c r="B3" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="182" t="s">
+      <c r="C3" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="182" t="s">
+      <c r="D3" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="182" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="173" t="s">
+      <c r="E3" s="171" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="167" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="173" t="s">
+      <c r="G3" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="173" t="s">
+      <c r="H3" s="167" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="J3" s="177" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="175" t="s">
+      <c r="J3" s="179" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="175" t="s">
+      <c r="L3" s="177" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="175" t="s">
-        <v>175</v>
-      </c>
-      <c r="N3" s="175" t="s">
+      <c r="M3" s="177" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" s="177" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="175" t="s">
+      <c r="O3" s="177" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="174"/>
-      <c r="B4" s="181"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="168"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="173"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="168"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="179"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="179"/>
-      <c r="O4" s="176"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J4" s="180"/>
+      <c r="K4" s="178"/>
+      <c r="L4" s="181"/>
+      <c r="M4" s="181"/>
+      <c r="N4" s="181"/>
+      <c r="O4" s="178"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3445,19 +3412,19 @@
       </c>
       <c r="L5" s="6">
         <f>N$1*F5%</f>
-        <v>134130</v>
+        <v>107830</v>
       </c>
       <c r="M5" s="23"/>
       <c r="N5" s="23">
         <f>L5+K5-J5+M5</f>
-        <v>134130.07195792551</v>
+        <v>107830.07195792551</v>
       </c>
       <c r="O5" s="23">
         <f>N5*6% + N5</f>
-        <v>142177.87627540104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>114299.87627540104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3469,7 +3436,7 @@
         <v>83</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F6" s="1">
         <v>3.33</v>
@@ -3493,20 +3460,20 @@
       </c>
       <c r="L6" s="6">
         <f t="shared" ref="L6:L40" si="2">N$1*F6%</f>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M6" s="23"/>
       <c r="N6" s="23">
         <f>L6+K6-J6+M6</f>
-        <v>387909.38216694933</v>
+        <v>354609.38216694933</v>
       </c>
       <c r="O6" s="23">
         <f t="shared" ref="O6:O40" si="3">N6*6% + N6</f>
-        <v>411183.94509696629</v>
+        <v>375885.94509696629</v>
       </c>
       <c r="Q6" s="31"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3522,17 +3489,17 @@
         <v>3.32</v>
       </c>
       <c r="G7" s="24">
-        <v>169307.54879999999</v>
+        <v>169327.54879999999</v>
       </c>
       <c r="H7" s="29">
-        <v>169300</v>
+        <v>169330</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="0"/>
-        <v>-7.5487999999895692</v>
+        <v>2.4512000000104308</v>
       </c>
       <c r="K7" s="38">
         <f t="shared" si="1"/>
@@ -3540,19 +3507,19 @@
       </c>
       <c r="L7" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="23">
         <f t="shared" ref="N7:N40" si="4">L7+K7-J7+M7</f>
-        <v>169327.54879999999</v>
+        <v>136117.54879999999</v>
       </c>
       <c r="O7" s="23">
         <f t="shared" si="3"/>
-        <v>179487.20172799999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144284.60172799998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -3568,18 +3535,18 @@
         <v>3.42</v>
       </c>
       <c r="G8" s="24">
-        <v>529509.1281354035</v>
+        <v>553929.1281354035</v>
       </c>
       <c r="H8" s="29">
-        <f>90000+60000</f>
-        <v>150000</v>
+        <f>180000+80000</f>
+        <v>260000</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="0"/>
-        <v>-379509.1281354035</v>
+        <v>-293929.1281354035</v>
       </c>
       <c r="K8" s="38">
         <f t="shared" si="1"/>
@@ -3587,19 +3554,19 @@
       </c>
       <c r="L8" s="6">
         <f t="shared" si="2"/>
-        <v>174420</v>
+        <v>140220</v>
       </c>
       <c r="M8" s="23"/>
       <c r="N8" s="23">
         <f t="shared" si="4"/>
-        <v>553929.1281354035</v>
+        <v>434149.1281354035</v>
       </c>
       <c r="O8" s="23">
         <f t="shared" si="3"/>
-        <v>587164.87582352769</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>460198.0758235277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3634,19 +3601,19 @@
       </c>
       <c r="L9" s="6">
         <f t="shared" si="2"/>
-        <v>170340</v>
+        <v>136940</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23">
         <f t="shared" si="4"/>
-        <v>170340</v>
+        <v>136940</v>
       </c>
       <c r="O9" s="23">
         <f t="shared" si="3"/>
-        <v>180560.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>145156.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3655,7 +3622,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="1">
@@ -3681,19 +3648,19 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23">
         <f t="shared" si="4"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="O10" s="23">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144721.79999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -3728,19 +3695,19 @@
       </c>
       <c r="L11" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23">
         <f t="shared" si="4"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="O11" s="23">
         <f t="shared" si="3"/>
-        <v>179479.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144287.20000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -3775,19 +3742,19 @@
       </c>
       <c r="L12" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="23">
         <f t="shared" si="4"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="O12" s="23">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144721.79999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -3799,7 +3766,7 @@
         <v>88</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F13" s="1">
         <v>3.24</v>
@@ -3823,74 +3790,74 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
+        <v>132840.00000000003</v>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="23">
         <f t="shared" si="4"/>
-        <v>262705.83373000496</v>
+        <v>230305.83373000499</v>
       </c>
       <c r="O13" s="23">
         <f t="shared" si="3"/>
-        <v>278468.18375380524</v>
+        <v>244124.18375380529</v>
       </c>
       <c r="R13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1"/>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="144" t="s">
+      <c r="D14" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="144" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" s="145">
+      <c r="E14" s="141" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="142">
         <v>3.33</v>
       </c>
-      <c r="G14" s="146">
-        <v>169300</v>
-      </c>
-      <c r="H14" s="147">
+      <c r="G14" s="143">
+        <v>169830.00000000003</v>
+      </c>
+      <c r="H14" s="144">
         <f>169300</f>
         <v>169300</v>
       </c>
-      <c r="I14" s="147" t="s">
+      <c r="I14" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="J14" s="148">
+      <c r="J14" s="145">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="149">
+        <v>-530.0000000000291</v>
+      </c>
+      <c r="K14" s="146">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="150">
+      <c r="L14" s="147">
         <f>N$1*F14%</f>
-        <v>169830.00000000003</v>
-      </c>
-      <c r="M14" s="151">
-        <v>0</v>
-      </c>
-      <c r="N14" s="152">
+        <v>136530</v>
+      </c>
+      <c r="M14" s="148">
+        <v>0</v>
+      </c>
+      <c r="N14" s="149">
         <f>L14+K14-J14+M14</f>
-        <v>169830.00000000003</v>
-      </c>
-      <c r="O14" s="152">
+        <v>137060.00000000003</v>
+      </c>
+      <c r="O14" s="149">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
+        <v>145283.60000000003</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -3925,19 +3892,19 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="23">
         <f t="shared" si="4"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="O15" s="23">
         <f t="shared" si="3"/>
-        <v>179479.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144287.20000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -3953,7 +3920,7 @@
         <v>3.33</v>
       </c>
       <c r="G16" s="24">
-        <v>169706.30077040006</v>
+        <v>169536.30077040009</v>
       </c>
       <c r="H16" s="29">
         <v>170000</v>
@@ -3963,7 +3930,7 @@
       </c>
       <c r="J16" s="7">
         <f t="shared" si="0"/>
-        <v>293.6992295999371</v>
+        <v>463.69922959990799</v>
       </c>
       <c r="K16" s="38">
         <f t="shared" si="1"/>
@@ -3971,19 +3938,19 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="23">
         <f t="shared" si="4"/>
-        <v>169536.30077040009</v>
+        <v>136066.30077040009</v>
       </c>
       <c r="O16" s="23">
         <f t="shared" si="3"/>
-        <v>179708.47881662409</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144230.27881662411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -3999,7 +3966,7 @@
         <v>3.24</v>
       </c>
       <c r="G17" s="24">
-        <v>165275.34635877245</v>
+        <v>165155.34635877248</v>
       </c>
       <c r="H17" s="29">
         <f>249000-H30</f>
@@ -4010,7 +3977,7 @@
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>84.65364122754545</v>
+        <v>204.65364122751635</v>
       </c>
       <c r="K17" s="38">
         <f t="shared" si="1"/>
@@ -4018,19 +3985,19 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
+        <v>132840.00000000003</v>
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="23">
         <f t="shared" si="4"/>
-        <v>165155.34635877248</v>
+        <v>132635.34635877251</v>
       </c>
       <c r="O17" s="23">
         <f t="shared" si="3"/>
-        <v>175064.66714029884</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>140593.46714029886</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -4042,13 +4009,13 @@
         <v>93</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F18" s="1">
         <v>3.33</v>
       </c>
       <c r="G18" s="24">
-        <v>179744.71643200007</v>
+        <v>174574.7164320001</v>
       </c>
       <c r="H18" s="29">
         <v>175000</v>
@@ -4058,7 +4025,7 @@
       </c>
       <c r="J18" s="7">
         <f t="shared" si="0"/>
-        <v>-4744.7164320000738</v>
+        <v>425.28356799989706</v>
       </c>
       <c r="K18" s="38">
         <f t="shared" si="1"/>
@@ -4066,19 +4033,19 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="23">
         <f t="shared" si="4"/>
-        <v>174574.7164320001</v>
+        <v>136104.7164320001</v>
       </c>
       <c r="O18" s="23">
         <f t="shared" si="3"/>
-        <v>185049.19941792011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144270.9994179201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -4094,15 +4061,15 @@
         <v>3.32</v>
       </c>
       <c r="G19" s="24">
-        <v>1141879.487381256</v>
+        <v>1404575.487381256</v>
       </c>
       <c r="H19" s="29"/>
       <c r="I19" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J19" s="7">
         <f>H19-G19</f>
-        <v>-1141879.487381256</v>
+        <v>-1404575.487381256</v>
       </c>
       <c r="K19" s="38">
         <f t="shared" si="1"/>
@@ -4110,22 +4077,19 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
-      </c>
-      <c r="M19" s="154">
-        <f>74376+19000</f>
-        <v>93376</v>
-      </c>
+        <v>136120</v>
+      </c>
+      <c r="M19" s="151"/>
       <c r="N19" s="23">
         <f t="shared" si="4"/>
-        <v>1404575.487381256</v>
+        <v>1540695.487381256</v>
       </c>
       <c r="O19" s="23">
         <f t="shared" si="3"/>
-        <v>1488850.0166241312</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1633137.2166241314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -4141,15 +4105,15 @@
         <v>3.33</v>
       </c>
       <c r="G20" s="13">
-        <v>2775460.7121669492</v>
+        <v>2945290.7121669492</v>
       </c>
       <c r="H20" s="29"/>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J20" s="41">
         <f t="shared" si="0"/>
-        <v>-2775460.7121669492</v>
+        <v>-2945290.7121669492</v>
       </c>
       <c r="K20" s="38">
         <f t="shared" si="1"/>
@@ -4157,20 +4121,20 @@
       </c>
       <c r="L20" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M20" s="6"/>
       <c r="N20" s="23">
         <f t="shared" si="4"/>
-        <v>2945290.7121669492</v>
+        <v>3081820.7121669492</v>
       </c>
       <c r="O20" s="23">
         <f t="shared" si="3"/>
-        <v>3122008.1548969662</v>
+        <v>3266729.954896966</v>
       </c>
       <c r="R20" s="30"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -4182,24 +4146,23 @@
         <v>96</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F21" s="1">
         <v>3.24</v>
       </c>
       <c r="G21" s="24">
-        <v>165240.00000000003</v>
+        <v>175154.40000000002</v>
       </c>
       <c r="H21" s="29">
-        <f>G21</f>
-        <v>165240.00000000003</v>
+        <v>165240</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J21" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-9914.4000000000233</v>
       </c>
       <c r="K21" s="38">
         <f t="shared" si="1"/>
@@ -4207,19 +4170,19 @@
       </c>
       <c r="L21" s="6">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
-      </c>
-      <c r="M21" s="154"/>
+        <v>132840.00000000003</v>
+      </c>
+      <c r="M21" s="151"/>
       <c r="N21" s="23">
         <f t="shared" si="4"/>
-        <v>165240.00000000003</v>
+        <v>142754.40000000005</v>
       </c>
       <c r="O21" s="23">
         <f t="shared" si="3"/>
-        <v>175154.40000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>151319.66400000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -4235,18 +4198,18 @@
         <v>3.24</v>
       </c>
       <c r="G22" s="24">
-        <v>164797.12080000006</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="H22" s="29">
-        <f>G22</f>
-        <v>164797.12080000006</v>
+        <f>176000</f>
+        <v>176000</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10759.999999999971</v>
       </c>
       <c r="K22" s="38">
         <f t="shared" si="1"/>
@@ -4254,19 +4217,19 @@
       </c>
       <c r="L22" s="6">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
+        <v>132840.00000000003</v>
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="23">
         <f t="shared" si="4"/>
-        <v>165240.00000000003</v>
+        <v>122080.00000000006</v>
       </c>
       <c r="O22" s="23">
         <f t="shared" si="3"/>
-        <v>175154.40000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>129404.80000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -4278,20 +4241,20 @@
         <v>98</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1">
         <v>3.32</v>
       </c>
       <c r="G23" s="24">
-        <v>169312.47794799984</v>
+        <v>169320.47794799984</v>
       </c>
       <c r="H23" s="29">
-        <f>252952-H31</f>
-        <v>169312</v>
+        <f>252960-H31</f>
+        <v>169320</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
@@ -4303,19 +4266,19 @@
       </c>
       <c r="L23" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="23">
         <f t="shared" si="4"/>
-        <v>169320.47794799984</v>
+        <v>136120.47794799984</v>
       </c>
       <c r="O23" s="23">
         <f t="shared" si="3"/>
-        <v>179479.70662487982</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144287.70662487982</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -4327,7 +4290,7 @@
         <v>99</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="1">
         <v>3.33</v>
@@ -4340,7 +4303,7 @@
         <v>169830.00000000003</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
@@ -4352,19 +4315,19 @@
       </c>
       <c r="L24" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="23">
         <f t="shared" si="4"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="O24" s="23">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144721.79999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -4376,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="1">
         <v>3.24</v>
@@ -4389,7 +4352,7 @@
         <v>165240.00000000003</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
@@ -4401,19 +4364,19 @@
       </c>
       <c r="L25" s="6">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
+        <v>132840.00000000003</v>
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="23">
         <f t="shared" si="4"/>
-        <v>165240.00000000003</v>
+        <v>132840.00000000003</v>
       </c>
       <c r="O25" s="23">
         <f t="shared" si="3"/>
-        <v>175154.40000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>140810.40000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -4429,14 +4392,14 @@
         <v>3.33</v>
       </c>
       <c r="G26" s="24">
-        <v>169830.44620100007</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="H26" s="29">
         <f>G26</f>
-        <v>169830.44620100007</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="0"/>
@@ -4448,19 +4411,19 @@
       </c>
       <c r="L26" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="23">
         <f t="shared" si="4"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="O26" s="23">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144721.79999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -4472,23 +4435,23 @@
         <v>102</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F27" s="1">
         <v>3.32</v>
       </c>
       <c r="G27" s="17">
-        <v>169313.77491239994</v>
+        <v>168633.77491239994</v>
       </c>
       <c r="H27" s="29">
         <v>170000</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
-        <v>686.22508760006167</v>
+        <v>1366.2250876000617</v>
       </c>
       <c r="K27" s="38">
         <f t="shared" si="1"/>
@@ -4496,22 +4459,22 @@
       </c>
       <c r="L27" s="6">
         <f t="shared" si="2"/>
-        <v>169320</v>
+        <v>136120</v>
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="23">
         <f t="shared" si="4"/>
-        <v>168633.77491239994</v>
+        <v>134753.77491239994</v>
       </c>
       <c r="O27" s="23">
         <f t="shared" si="3"/>
-        <v>178751.80140714394</v>
-      </c>
-      <c r="Q27" s="143" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>142839.00140714392</v>
+      </c>
+      <c r="Q27" s="140" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -4523,7 +4486,7 @@
         <v>103</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F28" s="1">
         <v>3.33</v>
@@ -4536,7 +4499,7 @@
         <v>169830.00000000003</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J28" s="7">
         <f t="shared" si="0"/>
@@ -4548,71 +4511,69 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="2"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="23">
         <f t="shared" si="4"/>
-        <v>169830.00000000003</v>
+        <v>136530</v>
       </c>
       <c r="O28" s="23">
         <f t="shared" si="3"/>
-        <v>180019.80000000002</v>
-      </c>
-      <c r="Q28" s="143"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>144721.79999999999</v>
+      </c>
+      <c r="Q28" s="140"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="140" t="s">
-        <v>174</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="D29" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="142">
         <v>3.24</v>
       </c>
-      <c r="G29" s="24">
-        <v>899519.05374809331</v>
-      </c>
-      <c r="H29" s="29">
-        <v>165240</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J29" s="7">
+      <c r="G29" s="143">
+        <v>165240.00000000003</v>
+      </c>
+      <c r="H29" s="144">
+        <f>G29</f>
+        <v>165240.00000000003</v>
+      </c>
+      <c r="I29" s="144" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="145">
         <f t="shared" si="0"/>
-        <v>-734279.05374809331</v>
-      </c>
-      <c r="K29" s="38">
+        <v>0</v>
+      </c>
+      <c r="K29" s="146">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="147">
         <f t="shared" si="2"/>
-        <v>165240.00000000003</v>
-      </c>
-      <c r="M29" s="154">
-        <f>74376+19000</f>
-        <v>93376</v>
-      </c>
-      <c r="N29" s="23">
+        <v>132840.00000000003</v>
+      </c>
+      <c r="M29" s="195"/>
+      <c r="N29" s="149">
         <f>L29+K29-J29+M29</f>
-        <v>992895.05374809331</v>
-      </c>
-      <c r="O29" s="23">
+        <v>132840.00000000003</v>
+      </c>
+      <c r="O29" s="149">
         <f t="shared" si="3"/>
-        <v>1052468.7569729788</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>140810.40000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -4635,7 +4596,7 @@
         <v>83639.999999999985</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J30" s="7">
         <f t="shared" si="0"/>
@@ -4647,19 +4608,19 @@
       </c>
       <c r="L30" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O30" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -4682,7 +4643,7 @@
         <v>83639.999999999985</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
@@ -4694,19 +4655,19 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O31" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -4722,17 +4683,17 @@
         <v>1.64</v>
       </c>
       <c r="G32" s="24">
-        <v>208309.73443736718</v>
+        <v>226949.73443736718</v>
       </c>
       <c r="H32" s="29">
         <v>65000</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J32" s="7">
         <f t="shared" si="0"/>
-        <v>-143309.73443736718</v>
+        <v>-161949.73443736718</v>
       </c>
       <c r="K32" s="38">
         <f t="shared" si="1"/>
@@ -4740,19 +4701,19 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="23">
         <f t="shared" si="4"/>
-        <v>226949.73443736718</v>
+        <v>229189.73443736718</v>
       </c>
       <c r="O32" s="23">
         <f t="shared" si="3"/>
-        <v>240566.71850360921</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>242941.11850360921</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -4768,15 +4729,15 @@
         <v>1.64</v>
       </c>
       <c r="G33" s="24">
-        <v>469026.30447480001</v>
+        <v>552666.30447480001</v>
       </c>
       <c r="H33" s="29"/>
       <c r="I33" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J33" s="7">
         <f t="shared" si="0"/>
-        <v>-469026.30447480001</v>
+        <v>-552666.30447480001</v>
       </c>
       <c r="K33" s="38">
         <f t="shared" si="1"/>
@@ -4784,22 +4745,22 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="23">
         <f t="shared" si="4"/>
-        <v>552666.30447480001</v>
+        <v>619906.30447480001</v>
       </c>
       <c r="O33" s="23">
         <f t="shared" si="3"/>
-        <v>585826.28274328797</v>
+        <v>657100.68274328799</v>
       </c>
       <c r="Q33" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -4815,15 +4776,18 @@
         <v>1.64</v>
       </c>
       <c r="G34" s="24">
-        <v>83639.999999999985</v>
-      </c>
-      <c r="H34" s="29"/>
+        <v>167279.99999999997</v>
+      </c>
+      <c r="H34" s="29">
+        <f>G34</f>
+        <v>167279.99999999997</v>
+      </c>
       <c r="I34" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
-        <v>-83639.999999999985</v>
+        <v>0</v>
       </c>
       <c r="K34" s="38">
         <f t="shared" si="1"/>
@@ -4831,19 +4795,19 @@
       </c>
       <c r="L34" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="23">
         <f t="shared" si="4"/>
-        <v>167279.99999999997</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O34" s="23">
         <f t="shared" si="3"/>
-        <v>177316.79999999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -4876,19 +4840,19 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O35" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -4903,16 +4867,16 @@
       <c r="F36" s="1">
         <v>1.64</v>
       </c>
-      <c r="G36" s="142">
-        <v>1322074.7826287674</v>
+      <c r="G36" s="139">
+        <v>1405714.7826287674</v>
       </c>
       <c r="H36" s="29"/>
       <c r="I36" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J36" s="7">
         <f t="shared" si="0"/>
-        <v>-1322074.7826287674</v>
+        <v>-1405714.7826287674</v>
       </c>
       <c r="K36" s="38">
         <f t="shared" si="1"/>
@@ -4920,19 +4884,19 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="23">
         <f t="shared" si="4"/>
-        <v>1405714.7826287674</v>
+        <v>1472954.7826287674</v>
       </c>
       <c r="O36" s="23">
         <f t="shared" si="3"/>
-        <v>1490057.6695864934</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1561332.0695864935</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
@@ -4955,7 +4919,7 @@
         <v>83639.999999999985</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J37" s="7">
         <f t="shared" si="0"/>
@@ -4967,19 +4931,19 @@
       </c>
       <c r="L37" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O37" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
@@ -4995,15 +4959,18 @@
         <v>1.64</v>
       </c>
       <c r="G38" s="24">
-        <v>83639.999999999985</v>
-      </c>
-      <c r="H38" s="29"/>
+        <v>167279.99999999997</v>
+      </c>
+      <c r="H38" s="29">
+        <f>G38</f>
+        <v>167279.99999999997</v>
+      </c>
       <c r="I38" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
-        <v>-83639.999999999985</v>
+        <v>0</v>
       </c>
       <c r="K38" s="38">
         <f t="shared" si="1"/>
@@ -5011,19 +4978,19 @@
       </c>
       <c r="L38" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="23">
         <f t="shared" si="4"/>
-        <v>167279.99999999997</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O38" s="23">
         <f t="shared" si="3"/>
-        <v>177316.79999999996</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>34</v>
       </c>
@@ -5039,14 +5006,14 @@
         <v>1.64</v>
       </c>
       <c r="G39" s="24">
-        <v>83640.001605599842</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="H39" s="29">
         <f>G39</f>
-        <v>83640.001605599842</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J39" s="7">
         <f>H39-G39</f>
@@ -5058,19 +5025,19 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="O39" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>71274.39999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>34</v>
       </c>
@@ -5086,15 +5053,17 @@
         <v>1.64</v>
       </c>
       <c r="G40" s="24">
-        <v>352508.98363898392</v>
-      </c>
-      <c r="H40" s="29"/>
+        <v>436148.98363898392</v>
+      </c>
+      <c r="H40" s="29">
+        <v>200000</v>
+      </c>
       <c r="I40" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J40" s="7">
         <f t="shared" si="0"/>
-        <v>-352508.98363898392</v>
+        <v>-236148.98363898392</v>
       </c>
       <c r="K40" s="38">
         <f t="shared" si="1"/>
@@ -5102,19 +5071,19 @@
       </c>
       <c r="L40" s="6">
         <f t="shared" si="2"/>
-        <v>83639.999999999985</v>
+        <v>67239.999999999985</v>
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="23">
         <f t="shared" si="4"/>
-        <v>436148.98363898392</v>
+        <v>303388.98363898392</v>
       </c>
       <c r="O40" s="23">
         <f t="shared" si="3"/>
-        <v>462317.92265732295</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>321592.32265732298</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -5126,16 +5095,16 @@
       </c>
       <c r="G41" s="9">
         <f>SUM(G5:G40)</f>
-        <v>12113881.208294673</v>
+        <v>12278162.98593998</v>
       </c>
       <c r="H41" s="9">
         <f>SUM(H5:H40)</f>
-        <v>4309319.5686066002</v>
+        <v>4965120</v>
       </c>
       <c r="I41" s="9"/>
-      <c r="J41" s="135">
+      <c r="J41" s="133">
         <f t="shared" ref="J41:O41" si="5">SUM(J5:J40)</f>
-        <v>-7804561.6396880727</v>
+        <v>-7313042.9859399796</v>
       </c>
       <c r="K41" s="9">
         <f t="shared" si="5"/>
@@ -5143,139 +5112,133 @@
       </c>
       <c r="L41" s="9">
         <f t="shared" si="5"/>
-        <v>5104590</v>
+        <v>4103690</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="5"/>
-        <v>186752</v>
+        <v>0</v>
       </c>
       <c r="N41" s="10">
         <f t="shared" si="5"/>
-        <v>13095903.639688073</v>
+        <v>11416732.98593998</v>
       </c>
       <c r="O41" s="9">
         <f t="shared" si="5"/>
-        <v>13881657.858069362</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>12101736.965096382</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" t="s">
         <v>117</v>
       </c>
       <c r="I42">
         <f>SUMIF(I5:I40,"b",H5:H40)</f>
-        <v>4055849.1224055998</v>
+        <v>4711650</v>
       </c>
       <c r="L42" s="11"/>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" t="s">
         <v>118</v>
       </c>
       <c r="I43">
         <f>SUMIF(I5:I40,"e",H5:H40)</f>
-        <v>169830.44620100007</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>169830.00000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="35">
         <f>I42+I43</f>
-        <v>4225679.5686066002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="170" t="s">
-        <v>176</v>
-      </c>
-      <c r="E47" s="170"/>
-      <c r="F47" s="170"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="170"/>
-      <c r="I47" s="170"/>
-      <c r="J47" s="170"/>
-      <c r="K47" s="170"/>
-      <c r="L47" s="170"/>
-      <c r="M47" s="170"/>
-      <c r="N47" s="170"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D48" s="170"/>
-      <c r="E48" s="170"/>
-      <c r="F48" s="170"/>
-      <c r="G48" s="170"/>
-      <c r="H48" s="170"/>
-      <c r="I48" s="170"/>
-      <c r="J48" s="170"/>
-      <c r="K48" s="170"/>
-      <c r="L48" s="170"/>
-      <c r="M48" s="170"/>
-      <c r="N48" s="170"/>
-    </row>
-    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D49" s="170"/>
-      <c r="E49" s="170"/>
-      <c r="F49" s="170"/>
-      <c r="G49" s="170"/>
-      <c r="H49" s="170"/>
-      <c r="I49" s="170"/>
-      <c r="J49" s="170"/>
-      <c r="K49" s="170"/>
-      <c r="L49" s="170"/>
-      <c r="M49" s="170"/>
-      <c r="N49" s="170"/>
-    </row>
-    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D50" s="170"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="170"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="170"/>
-      <c r="J50" s="170"/>
-      <c r="K50" s="170"/>
-      <c r="L50" s="170"/>
-      <c r="M50" s="170"/>
-      <c r="N50" s="170"/>
-    </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D51" s="170"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="170"/>
-      <c r="G51" s="170"/>
-      <c r="H51" s="170"/>
-      <c r="I51" s="170"/>
-      <c r="J51" s="170"/>
-      <c r="K51" s="170"/>
-      <c r="L51" s="170"/>
-      <c r="M51" s="170"/>
-      <c r="N51" s="170"/>
-    </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D52" s="153"/>
-      <c r="E52" s="153"/>
-      <c r="F52" s="153"/>
-      <c r="G52" s="153"/>
-      <c r="H52" s="153"/>
-      <c r="I52" s="153"/>
-      <c r="J52" s="153"/>
-      <c r="K52" s="153"/>
-      <c r="L52" s="153"/>
-      <c r="M52" s="153"/>
-      <c r="N52" s="153"/>
+        <v>4881480</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="174" t="s">
+        <v>174</v>
+      </c>
+      <c r="E47" s="174"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="174"/>
+      <c r="H47" s="174"/>
+      <c r="I47" s="174"/>
+      <c r="J47" s="174"/>
+      <c r="K47" s="174"/>
+      <c r="L47" s="174"/>
+      <c r="M47" s="174"/>
+      <c r="N47" s="174"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D48" s="174"/>
+      <c r="E48" s="174"/>
+      <c r="F48" s="174"/>
+      <c r="G48" s="174"/>
+      <c r="H48" s="174"/>
+      <c r="I48" s="174"/>
+      <c r="J48" s="174"/>
+      <c r="K48" s="174"/>
+      <c r="L48" s="174"/>
+      <c r="M48" s="174"/>
+      <c r="N48" s="174"/>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D49" s="174"/>
+      <c r="E49" s="174"/>
+      <c r="F49" s="174"/>
+      <c r="G49" s="174"/>
+      <c r="H49" s="174"/>
+      <c r="I49" s="174"/>
+      <c r="J49" s="174"/>
+      <c r="K49" s="174"/>
+      <c r="L49" s="174"/>
+      <c r="M49" s="174"/>
+      <c r="N49" s="174"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D50" s="174"/>
+      <c r="E50" s="174"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="174"/>
+      <c r="H50" s="174"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="174"/>
+      <c r="K50" s="174"/>
+      <c r="L50" s="174"/>
+      <c r="M50" s="174"/>
+      <c r="N50" s="174"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D51" s="174"/>
+      <c r="E51" s="174"/>
+      <c r="F51" s="174"/>
+      <c r="G51" s="174"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="174"/>
+      <c r="K51" s="174"/>
+      <c r="L51" s="174"/>
+      <c r="M51" s="174"/>
+      <c r="N51" s="174"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D52" s="150"/>
+      <c r="E52" s="150"/>
+      <c r="F52" s="150"/>
+      <c r="G52" s="150"/>
+      <c r="H52" s="150"/>
+      <c r="I52" s="150"/>
+      <c r="J52" s="150"/>
+      <c r="K52" s="150"/>
+      <c r="L52" s="150"/>
+      <c r="M52" s="150"/>
+      <c r="N52" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="D47:N51"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N1:O1"/>
@@ -5287,6 +5250,12 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5296,64 +5265,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E6:O38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="192" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="191"/>
+    <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="189" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="188"/>
       <c r="L7" s="42"/>
       <c r="M7" s="43"/>
     </row>
-    <row r="8" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="194" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" s="193"/>
-      <c r="G8" s="193"/>
-      <c r="H8" s="193"/>
-      <c r="I8" s="193"/>
-      <c r="J8" s="193"/>
-      <c r="K8" s="191"/>
+    <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="190"/>
+      <c r="G8" s="190"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="190"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="188"/>
       <c r="L8" s="44"/>
       <c r="M8" s="45"/>
     </row>
-    <row r="9" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E9" s="42"/>
       <c r="F9" s="46"/>
       <c r="G9" s="46"/>
       <c r="H9" s="46"/>
       <c r="I9" s="47"/>
       <c r="J9" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K9" s="45"/>
       <c r="L9" s="44"/>
       <c r="M9" s="45"/>
     </row>
-    <row r="10" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E10" s="44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
       <c r="I10" s="47"/>
       <c r="J10" s="47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K10" s="45"/>
       <c r="L10" s="44"/>
       <c r="M10" s="45"/>
     </row>
-    <row r="11" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E11" s="48"/>
       <c r="F11" s="49"/>
       <c r="G11" s="49"/>
@@ -5364,20 +5333,20 @@
       <c r="L11" s="44"/>
       <c r="M11" s="45"/>
     </row>
-    <row r="12" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="195" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
-      <c r="J12" s="196"/>
-      <c r="K12" s="197"/>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="192" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="193"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="193"/>
+      <c r="J12" s="193"/>
+      <c r="K12" s="194"/>
       <c r="L12" s="44"/>
       <c r="M12" s="45"/>
     </row>
-    <row r="13" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E13" s="44"/>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
@@ -5388,9 +5357,9 @@
       <c r="L13" s="44"/>
       <c r="M13" s="45"/>
     </row>
-    <row r="14" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E14" s="44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47" t="str">
@@ -5399,20 +5368,20 @@
       </c>
       <c r="H14" s="47"/>
       <c r="I14" s="47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J14" s="51">
         <v>45600</v>
       </c>
       <c r="K14" s="45"/>
-      <c r="L14" s="185" t="s">
-        <v>158</v>
-      </c>
-      <c r="M14" s="186"/>
-    </row>
-    <row r="15" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L14" s="182" t="s">
+        <v>156</v>
+      </c>
+      <c r="M14" s="183"/>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E15" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F15" s="52" t="str">
         <f>PRORRATEO!C10</f>
@@ -5426,7 +5395,7 @@
       <c r="L15" s="44"/>
       <c r="M15" s="45"/>
     </row>
-    <row r="16" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E16" s="44"/>
       <c r="F16" s="47"/>
       <c r="G16" s="47"/>
@@ -5434,10 +5403,10 @@
       <c r="I16" s="47"/>
       <c r="J16" s="47"/>
       <c r="K16" s="45"/>
-      <c r="L16" s="187"/>
-      <c r="M16" s="186"/>
-    </row>
-    <row r="17" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="L16" s="184"/>
+      <c r="M16" s="183"/>
+    </row>
+    <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" s="44"/>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
@@ -5448,7 +5417,7 @@
       <c r="L17" s="44"/>
       <c r="M17" s="45"/>
     </row>
-    <row r="18" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E18" s="44"/>
       <c r="F18" s="47"/>
       <c r="G18" s="47"/>
@@ -5459,7 +5428,7 @@
       <c r="L18" s="44"/>
       <c r="M18" s="45"/>
     </row>
-    <row r="19" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E19" s="44"/>
       <c r="F19" s="47"/>
       <c r="G19" s="47"/>
@@ -5470,78 +5439,78 @@
       <c r="L19" s="53"/>
       <c r="M19" s="54"/>
     </row>
-    <row r="20" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="188" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="190">
+    <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="185" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="186"/>
+      <c r="G20" s="186"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="187">
         <f>PRORRATEO!H10</f>
         <v>169830.00000000003</v>
       </c>
-      <c r="K20" s="191"/>
+      <c r="K20" s="188"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
     </row>
-    <row r="24" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="192" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="193"/>
-      <c r="I25" s="193"/>
-      <c r="J25" s="193"/>
-      <c r="K25" s="193"/>
-      <c r="L25" s="193"/>
-      <c r="M25" s="191"/>
+    <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="189" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="190"/>
+      <c r="I25" s="190"/>
+      <c r="J25" s="190"/>
+      <c r="K25" s="190"/>
+      <c r="L25" s="190"/>
+      <c r="M25" s="188"/>
       <c r="N25" s="42"/>
       <c r="O25" s="43"/>
     </row>
-    <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G26" s="194" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" s="193"/>
-      <c r="I26" s="193"/>
-      <c r="J26" s="193"/>
-      <c r="K26" s="193"/>
-      <c r="L26" s="193"/>
-      <c r="M26" s="191"/>
+    <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="190"/>
+      <c r="I26" s="190"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="190"/>
+      <c r="L26" s="190"/>
+      <c r="M26" s="188"/>
       <c r="N26" s="44"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G27" s="42"/>
       <c r="H27" s="46"/>
       <c r="I27" s="46"/>
       <c r="J27" s="46"/>
       <c r="K27" s="47"/>
       <c r="L27" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M27" s="45"/>
       <c r="N27" s="44"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G28" s="44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H28" s="47"/>
       <c r="I28" s="47"/>
       <c r="J28" s="47"/>
       <c r="K28" s="47"/>
       <c r="L28" s="47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M28" s="45"/>
       <c r="N28" s="44"/>
       <c r="O28" s="45"/>
     </row>
-    <row r="29" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G29" s="48"/>
       <c r="H29" s="49"/>
       <c r="I29" s="49"/>
@@ -5552,20 +5521,20 @@
       <c r="N29" s="44"/>
       <c r="O29" s="45"/>
     </row>
-    <row r="30" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G30" s="195" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="196"/>
-      <c r="I30" s="196"/>
-      <c r="J30" s="196"/>
-      <c r="K30" s="196"/>
-      <c r="L30" s="196"/>
-      <c r="M30" s="197"/>
+    <row r="30" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G30" s="192" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="193"/>
+      <c r="I30" s="193"/>
+      <c r="J30" s="193"/>
+      <c r="K30" s="193"/>
+      <c r="L30" s="193"/>
+      <c r="M30" s="194"/>
       <c r="N30" s="44"/>
       <c r="O30" s="45"/>
     </row>
-    <row r="31" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G31" s="44"/>
       <c r="H31" s="47"/>
       <c r="I31" s="47"/>
@@ -5576,28 +5545,28 @@
       <c r="N31" s="44"/>
       <c r="O31" s="45"/>
     </row>
-    <row r="32" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G32" s="44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H32" s="47"/>
       <c r="I32" s="47"/>
       <c r="J32" s="47"/>
       <c r="K32" s="47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L32" s="51">
         <v>45600</v>
       </c>
       <c r="M32" s="45"/>
-      <c r="N32" s="185" t="s">
-        <v>158</v>
-      </c>
-      <c r="O32" s="186"/>
-    </row>
-    <row r="33" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="N32" s="182" t="s">
+        <v>156</v>
+      </c>
+      <c r="O32" s="183"/>
+    </row>
+    <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H33" s="52" t="str">
         <f>PRORRATEO!E28</f>
@@ -5611,7 +5580,7 @@
       <c r="N33" s="44"/>
       <c r="O33" s="45"/>
     </row>
-    <row r="34" spans="7:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G34" s="44"/>
       <c r="H34" s="47"/>
       <c r="I34" s="47"/>
@@ -5619,10 +5588,10 @@
       <c r="K34" s="47"/>
       <c r="L34" s="47"/>
       <c r="M34" s="45"/>
-      <c r="N34" s="187"/>
-      <c r="O34" s="186"/>
-    </row>
-    <row r="35" spans="7:15" x14ac:dyDescent="0.3">
+      <c r="N34" s="184"/>
+      <c r="O34" s="183"/>
+    </row>
+    <row r="35" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G35" s="44"/>
       <c r="H35" s="47"/>
       <c r="I35" s="47"/>
@@ -5633,7 +5602,7 @@
       <c r="N35" s="44"/>
       <c r="O35" s="45"/>
     </row>
-    <row r="36" spans="7:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G36" s="44"/>
       <c r="H36" s="47"/>
       <c r="I36" s="47"/>
@@ -5644,7 +5613,7 @@
       <c r="N36" s="44"/>
       <c r="O36" s="45"/>
     </row>
-    <row r="37" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G37" s="44"/>
       <c r="H37" s="47"/>
       <c r="I37" s="47"/>
@@ -5655,19 +5624,19 @@
       <c r="N37" s="53"/>
       <c r="O37" s="54"/>
     </row>
-    <row r="38" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="188" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="189"/>
-      <c r="K38" s="189"/>
-      <c r="L38" s="190">
+    <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="185" t="s">
+        <v>158</v>
+      </c>
+      <c r="H38" s="186"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="186"/>
+      <c r="K38" s="186"/>
+      <c r="L38" s="187">
         <f>PRORRATEO!J28</f>
         <v>0</v>
       </c>
-      <c r="M38" s="191"/>
+      <c r="M38" s="188"/>
       <c r="N38" s="55"/>
       <c r="O38" s="56"/>
     </row>

--- a/ALCORTA 146/Octubre/Octubre.xlsx
+++ b/ALCORTA 146/Octubre/Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BBDA5D-958B-49F6-B4F6-15F9AC4972ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CB0E3A-9893-4A30-A864-CC72A46CD6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1622,6 +1622,7 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1664,11 +1665,35 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1684,30 +1709,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1732,7 +1733,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2230,34 +2230,34 @@
       <c r="E14" s="69"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="154" t="s">
+      <c r="A15" s="155" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
+      <c r="B15" s="155"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
+      <c r="A16" s="155"/>
+      <c r="B16" s="155"/>
+      <c r="C16" s="155"/>
+      <c r="D16" s="155"/>
+      <c r="E16" s="155"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
+      <c r="A17" s="155"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="154"/>
-      <c r="B18" s="154"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="155"/>
+      <c r="C18" s="155"/>
+      <c r="D18" s="155"/>
+      <c r="E18" s="155"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69"/>
@@ -2281,39 +2281,39 @@
       <c r="E21" s="69"/>
     </row>
     <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="155"/>
-      <c r="B22" s="156"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
+      <c r="A22" s="156"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="156"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
+      <c r="A23" s="157"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="156"/>
-      <c r="B24" s="156"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
+      <c r="A24" s="157"/>
+      <c r="B24" s="157"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="157"/>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="156"/>
-      <c r="B25" s="156"/>
-      <c r="C25" s="156"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
+      <c r="A25" s="157"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="157"/>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="156"/>
-      <c r="B26" s="156"/>
-      <c r="C26" s="156"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
+      <c r="A26" s="157"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="157"/>
+      <c r="E26" s="157"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="69"/>
@@ -2845,40 +2845,40 @@
       <c r="F78" s="31"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="165" t="s">
+      <c r="A79" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="B79" s="166"/>
+      <c r="B79" s="167"/>
       <c r="C79" s="104"/>
       <c r="D79" s="69"/>
       <c r="E79" s="69"/>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="157"/>
-      <c r="B80" s="158"/>
+      <c r="A80" s="158"/>
+      <c r="B80" s="159"/>
       <c r="C80" s="17"/>
       <c r="D80" s="69"/>
       <c r="E80" s="69"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="159"/>
-      <c r="B81" s="160"/>
+      <c r="A81" s="160"/>
+      <c r="B81" s="161"/>
       <c r="C81" s="17"/>
       <c r="D81" s="69"/>
       <c r="E81" s="69"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="161"/>
-      <c r="B82" s="162"/>
+      <c r="A82" s="162"/>
+      <c r="B82" s="163"/>
       <c r="C82" s="105"/>
       <c r="D82" s="69"/>
       <c r="E82" s="106"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="163" t="s">
+      <c r="A83" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="B83" s="164"/>
+      <c r="B83" s="165"/>
       <c r="C83" s="107">
         <f>SUM(C80:C82)</f>
         <v>0</v>
@@ -2977,16 +2977,16 @@
       <c r="E92" s="69"/>
     </row>
     <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="156"/>
-      <c r="B93" s="156"/>
-      <c r="C93" s="156"/>
+      <c r="A93" s="157"/>
+      <c r="B93" s="157"/>
+      <c r="C93" s="157"/>
       <c r="D93" s="69"/>
       <c r="E93" s="69"/>
     </row>
     <row r="94" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="156"/>
-      <c r="B94" s="156"/>
-      <c r="C94" s="156"/>
+      <c r="A94" s="157"/>
+      <c r="B94" s="157"/>
+      <c r="C94" s="157"/>
       <c r="D94" s="69"/>
       <c r="E94" s="69"/>
     </row>
@@ -3204,16 +3204,16 @@
       <c r="E116" s="69"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="153" t="s">
+      <c r="A118" s="154" t="s">
         <v>147</v>
       </c>
-      <c r="B118" s="153"/>
-      <c r="C118" s="153"/>
+      <c r="B118" s="154"/>
+      <c r="C118" s="154"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="153"/>
-      <c r="B119" s="153"/>
-      <c r="C119" s="153"/>
+      <c r="A119" s="154"/>
+      <c r="B119" s="154"/>
+      <c r="C119" s="154"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
@@ -3290,10 +3290,10 @@
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="176">
+      <c r="N1" s="170">
         <v>4100000</v>
       </c>
-      <c r="O1" s="176"/>
+      <c r="O1" s="170"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3312,70 +3312,70 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="175"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="171" t="s">
+      <c r="D3" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="180" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="167" t="s">
+      <c r="F3" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="167" t="s">
+      <c r="G3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="167" t="s">
+      <c r="H3" s="171" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="J3" s="179" t="s">
+      <c r="J3" s="175" t="s">
         <v>134</v>
       </c>
-      <c r="K3" s="177" t="s">
+      <c r="K3" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="177" t="s">
+      <c r="L3" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="177" t="s">
+      <c r="M3" s="173" t="s">
         <v>173</v>
       </c>
-      <c r="N3" s="177" t="s">
+      <c r="N3" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="177" t="s">
+      <c r="O3" s="173" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="168"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="172"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="168"/>
+      <c r="A4" s="172"/>
+      <c r="B4" s="179"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="180"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="181"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="181"/>
-      <c r="O4" s="178"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="174"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="177"/>
+      <c r="N4" s="177"/>
+      <c r="O4" s="174"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -4563,7 +4563,7 @@
         <f t="shared" si="2"/>
         <v>132840.00000000003</v>
       </c>
-      <c r="M29" s="195"/>
+      <c r="M29" s="153"/>
       <c r="N29" s="149">
         <f>L29+K29-J29+M29</f>
         <v>132840.00000000003</v>
@@ -5158,71 +5158,71 @@
     <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="174" t="s">
+      <c r="D47" s="168" t="s">
         <v>174</v>
       </c>
-      <c r="E47" s="174"/>
-      <c r="F47" s="174"/>
-      <c r="G47" s="174"/>
-      <c r="H47" s="174"/>
-      <c r="I47" s="174"/>
-      <c r="J47" s="174"/>
-      <c r="K47" s="174"/>
-      <c r="L47" s="174"/>
-      <c r="M47" s="174"/>
-      <c r="N47" s="174"/>
+      <c r="E47" s="168"/>
+      <c r="F47" s="168"/>
+      <c r="G47" s="168"/>
+      <c r="H47" s="168"/>
+      <c r="I47" s="168"/>
+      <c r="J47" s="168"/>
+      <c r="K47" s="168"/>
+      <c r="L47" s="168"/>
+      <c r="M47" s="168"/>
+      <c r="N47" s="168"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D48" s="174"/>
-      <c r="E48" s="174"/>
-      <c r="F48" s="174"/>
-      <c r="G48" s="174"/>
-      <c r="H48" s="174"/>
-      <c r="I48" s="174"/>
-      <c r="J48" s="174"/>
-      <c r="K48" s="174"/>
-      <c r="L48" s="174"/>
-      <c r="M48" s="174"/>
-      <c r="N48" s="174"/>
+      <c r="D48" s="168"/>
+      <c r="E48" s="168"/>
+      <c r="F48" s="168"/>
+      <c r="G48" s="168"/>
+      <c r="H48" s="168"/>
+      <c r="I48" s="168"/>
+      <c r="J48" s="168"/>
+      <c r="K48" s="168"/>
+      <c r="L48" s="168"/>
+      <c r="M48" s="168"/>
+      <c r="N48" s="168"/>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D49" s="174"/>
-      <c r="E49" s="174"/>
-      <c r="F49" s="174"/>
-      <c r="G49" s="174"/>
-      <c r="H49" s="174"/>
-      <c r="I49" s="174"/>
-      <c r="J49" s="174"/>
-      <c r="K49" s="174"/>
-      <c r="L49" s="174"/>
-      <c r="M49" s="174"/>
-      <c r="N49" s="174"/>
+      <c r="D49" s="168"/>
+      <c r="E49" s="168"/>
+      <c r="F49" s="168"/>
+      <c r="G49" s="168"/>
+      <c r="H49" s="168"/>
+      <c r="I49" s="168"/>
+      <c r="J49" s="168"/>
+      <c r="K49" s="168"/>
+      <c r="L49" s="168"/>
+      <c r="M49" s="168"/>
+      <c r="N49" s="168"/>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D50" s="174"/>
-      <c r="E50" s="174"/>
-      <c r="F50" s="174"/>
-      <c r="G50" s="174"/>
-      <c r="H50" s="174"/>
-      <c r="I50" s="174"/>
-      <c r="J50" s="174"/>
-      <c r="K50" s="174"/>
-      <c r="L50" s="174"/>
-      <c r="M50" s="174"/>
-      <c r="N50" s="174"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="168"/>
+      <c r="F50" s="168"/>
+      <c r="G50" s="168"/>
+      <c r="H50" s="168"/>
+      <c r="I50" s="168"/>
+      <c r="J50" s="168"/>
+      <c r="K50" s="168"/>
+      <c r="L50" s="168"/>
+      <c r="M50" s="168"/>
+      <c r="N50" s="168"/>
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D51" s="174"/>
-      <c r="E51" s="174"/>
-      <c r="F51" s="174"/>
-      <c r="G51" s="174"/>
-      <c r="H51" s="174"/>
-      <c r="I51" s="174"/>
-      <c r="J51" s="174"/>
-      <c r="K51" s="174"/>
-      <c r="L51" s="174"/>
-      <c r="M51" s="174"/>
-      <c r="N51" s="174"/>
+      <c r="D51" s="168"/>
+      <c r="E51" s="168"/>
+      <c r="F51" s="168"/>
+      <c r="G51" s="168"/>
+      <c r="H51" s="168"/>
+      <c r="I51" s="168"/>
+      <c r="J51" s="168"/>
+      <c r="K51" s="168"/>
+      <c r="L51" s="168"/>
+      <c r="M51" s="168"/>
+      <c r="N51" s="168"/>
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D52" s="150"/>
@@ -5239,6 +5239,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="D47:N51"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N1:O1"/>
@@ -5250,12 +5256,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5269,28 +5269,28 @@
   <sheetData>
     <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="189" t="s">
+      <c r="E7" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="190"/>
-      <c r="G7" s="190"/>
-      <c r="H7" s="190"/>
-      <c r="I7" s="190"/>
-      <c r="J7" s="190"/>
-      <c r="K7" s="188"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="191"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="189"/>
       <c r="L7" s="42"/>
       <c r="M7" s="43"/>
     </row>
     <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="191" t="s">
+      <c r="E8" s="192" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
-      <c r="H8" s="190"/>
-      <c r="I8" s="190"/>
-      <c r="J8" s="190"/>
-      <c r="K8" s="188"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="189"/>
       <c r="L8" s="44"/>
       <c r="M8" s="45"/>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="M11" s="45"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E12" s="192" t="s">
+      <c r="E12" s="193" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="193"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="193"/>
-      <c r="J12" s="193"/>
-      <c r="K12" s="194"/>
+      <c r="F12" s="194"/>
+      <c r="G12" s="194"/>
+      <c r="H12" s="194"/>
+      <c r="I12" s="194"/>
+      <c r="J12" s="194"/>
+      <c r="K12" s="195"/>
       <c r="L12" s="44"/>
       <c r="M12" s="45"/>
     </row>
@@ -5374,10 +5374,10 @@
         <v>45600</v>
       </c>
       <c r="K14" s="45"/>
-      <c r="L14" s="182" t="s">
+      <c r="L14" s="183" t="s">
         <v>156</v>
       </c>
-      <c r="M14" s="183"/>
+      <c r="M14" s="184"/>
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E15" s="44" t="s">
@@ -5403,8 +5403,8 @@
       <c r="I16" s="47"/>
       <c r="J16" s="47"/>
       <c r="K16" s="45"/>
-      <c r="L16" s="184"/>
-      <c r="M16" s="183"/>
+      <c r="L16" s="185"/>
+      <c r="M16" s="184"/>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" s="44"/>
@@ -5440,45 +5440,45 @@
       <c r="M19" s="54"/>
     </row>
     <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="185" t="s">
+      <c r="E20" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="186"/>
-      <c r="G20" s="186"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="186"/>
-      <c r="J20" s="187">
+      <c r="F20" s="187"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="187"/>
+      <c r="I20" s="187"/>
+      <c r="J20" s="188">
         <f>PRORRATEO!H10</f>
         <v>169830.00000000003</v>
       </c>
-      <c r="K20" s="188"/>
+      <c r="K20" s="189"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
     </row>
     <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G25" s="189" t="s">
+      <c r="G25" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="H25" s="190"/>
-      <c r="I25" s="190"/>
-      <c r="J25" s="190"/>
-      <c r="K25" s="190"/>
-      <c r="L25" s="190"/>
-      <c r="M25" s="188"/>
+      <c r="H25" s="191"/>
+      <c r="I25" s="191"/>
+      <c r="J25" s="191"/>
+      <c r="K25" s="191"/>
+      <c r="L25" s="191"/>
+      <c r="M25" s="189"/>
       <c r="N25" s="42"/>
       <c r="O25" s="43"/>
     </row>
     <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G26" s="191" t="s">
+      <c r="G26" s="192" t="s">
         <v>149</v>
       </c>
-      <c r="H26" s="190"/>
-      <c r="I26" s="190"/>
-      <c r="J26" s="190"/>
-      <c r="K26" s="190"/>
-      <c r="L26" s="190"/>
-      <c r="M26" s="188"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="189"/>
       <c r="N26" s="44"/>
       <c r="O26" s="45"/>
     </row>
@@ -5522,15 +5522,15 @@
       <c r="O29" s="45"/>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="G30" s="192" t="s">
+      <c r="G30" s="193" t="s">
         <v>153</v>
       </c>
-      <c r="H30" s="193"/>
-      <c r="I30" s="193"/>
-      <c r="J30" s="193"/>
-      <c r="K30" s="193"/>
-      <c r="L30" s="193"/>
-      <c r="M30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="194"/>
+      <c r="L30" s="194"/>
+      <c r="M30" s="195"/>
       <c r="N30" s="44"/>
       <c r="O30" s="45"/>
     </row>
@@ -5559,10 +5559,10 @@
         <v>45600</v>
       </c>
       <c r="M32" s="45"/>
-      <c r="N32" s="182" t="s">
+      <c r="N32" s="183" t="s">
         <v>156</v>
       </c>
-      <c r="O32" s="183"/>
+      <c r="O32" s="184"/>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="44" t="s">
@@ -5588,8 +5588,8 @@
       <c r="K34" s="47"/>
       <c r="L34" s="47"/>
       <c r="M34" s="45"/>
-      <c r="N34" s="184"/>
-      <c r="O34" s="183"/>
+      <c r="N34" s="185"/>
+      <c r="O34" s="184"/>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G35" s="44"/>
@@ -5625,18 +5625,18 @@
       <c r="O37" s="54"/>
     </row>
     <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G38" s="185" t="s">
+      <c r="G38" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="H38" s="186"/>
-      <c r="I38" s="186"/>
-      <c r="J38" s="186"/>
-      <c r="K38" s="186"/>
-      <c r="L38" s="187">
+      <c r="H38" s="187"/>
+      <c r="I38" s="187"/>
+      <c r="J38" s="187"/>
+      <c r="K38" s="187"/>
+      <c r="L38" s="188">
         <f>PRORRATEO!J28</f>
         <v>0</v>
       </c>
-      <c r="M38" s="188"/>
+      <c r="M38" s="189"/>
       <c r="N38" s="55"/>
       <c r="O38" s="56"/>
     </row>
